--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.77974582738461</v>
+        <v>4.18920869695</v>
       </c>
       <c r="D2" t="n">
-        <v>24.41677727190218</v>
+        <v>3.967726306684105</v>
       </c>
       <c r="E2" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F2" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.02557475683916</v>
+        <v>7.479155897986364</v>
       </c>
       <c r="D3" t="n">
-        <v>34.51688482165641</v>
+        <v>5.608993783519167</v>
       </c>
       <c r="E3" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F3" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.14892837054976</v>
+        <v>2.624200860214336</v>
       </c>
       <c r="D4" t="n">
-        <v>15.28838015949481</v>
+        <v>2.484361775917907</v>
       </c>
       <c r="E4" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F4" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.80021502561981</v>
+        <v>9.717534941663219</v>
       </c>
       <c r="D5" t="n">
-        <v>41.8359892915179</v>
+        <v>6.798348259871658</v>
       </c>
       <c r="E5" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F5" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.43875403167838</v>
+        <v>1.696297530147737</v>
       </c>
       <c r="D6" t="n">
-        <v>11.5047553834695</v>
+        <v>1.869522749813794</v>
       </c>
       <c r="E6" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F6" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.49284089364613</v>
+        <v>6.905086645217497</v>
       </c>
       <c r="D7" t="n">
-        <v>25.15061745684232</v>
+        <v>4.086975336736876</v>
       </c>
       <c r="E7" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F7" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>75.63226929651618</v>
+        <v>12.29024376068388</v>
       </c>
       <c r="D8" t="n">
-        <v>57.07870172841108</v>
+        <v>9.275289030866801</v>
       </c>
       <c r="E8" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F8" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.70976836050203</v>
+        <v>4.01533735858158</v>
       </c>
       <c r="D9" t="n">
-        <v>11.31363951723363</v>
+        <v>1.838466421550466</v>
       </c>
       <c r="E9" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F9" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.42184562395486</v>
+        <v>2.831049913892664</v>
       </c>
       <c r="D10" t="n">
-        <v>4.031128874149275</v>
+        <v>0.6550584420492571</v>
       </c>
       <c r="E10" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F10" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>56.04683338500723</v>
+        <v>9.107610425063676</v>
       </c>
       <c r="D11" t="n">
-        <v>37.4254996075486</v>
+        <v>6.081643686226648</v>
       </c>
       <c r="E11" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F11" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>71.64474441840592</v>
+        <v>11.64227096799096</v>
       </c>
       <c r="D12" t="n">
-        <v>53.02300926698011</v>
+        <v>8.616239005884267</v>
       </c>
       <c r="E12" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F12" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.17505707795005</v>
+        <v>5.065946775166884</v>
       </c>
       <c r="D13" t="n">
-        <v>30.76002295749597</v>
+        <v>4.998503730593095</v>
       </c>
       <c r="E13" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F13" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>11.64468037380199</v>
+        <v>1.892260560742823</v>
       </c>
       <c r="D14" t="n">
-        <v>12.98258786208442</v>
+        <v>2.109670527588718</v>
       </c>
       <c r="E14" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F14" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>26.46100788937484</v>
+        <v>4.299913782023411</v>
       </c>
       <c r="D15" t="n">
-        <v>22.19234102117215</v>
+        <v>3.606255415940474</v>
       </c>
       <c r="E15" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F15" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>51.38310223768828</v>
+        <v>8.349754113624344</v>
       </c>
       <c r="D16" t="n">
-        <v>44.07096549884061</v>
+        <v>7.1615318935616</v>
       </c>
       <c r="E16" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F16" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>15.46302920840022</v>
+        <v>2.512742246365037</v>
       </c>
       <c r="D17" t="n">
-        <v>2.348557434691653</v>
+        <v>0.3816405831373936</v>
       </c>
       <c r="E17" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F17" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>65.56772479263286</v>
+        <v>10.65475527880284</v>
       </c>
       <c r="D18" t="n">
-        <v>61.47984666010306</v>
+        <v>9.990475082266748</v>
       </c>
       <c r="E18" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F18" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>24.14676939600481</v>
+        <v>3.923850026850781</v>
       </c>
       <c r="D19" t="n">
-        <v>29.14369232756575</v>
+        <v>4.735850003229435</v>
       </c>
       <c r="E19" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F19" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>26.4490023794205</v>
+        <v>4.297962886655831</v>
       </c>
       <c r="D20" t="n">
-        <v>30.35905772299501</v>
+        <v>4.933346879986689</v>
       </c>
       <c r="E20" t="n">
-        <v>20.56778587268821</v>
+        <v>3.342265204311835</v>
       </c>
       <c r="F20" t="n">
-        <v>16.85524678748426</v>
+        <v>2.738977602966193</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
